--- a/results/operaciones_20240229.xlsx
+++ b/results/operaciones_20240229.xlsx
@@ -446,77 +446,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>IWDA.L</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="C2" t="n">
-        <v>189.3099975585938</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001433207289325578</v>
+        <v>0.002764284479290566</v>
       </c>
       <c r="E2" t="n">
-        <v>189.5813180270369</v>
+        <v>95.56343937107013</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>931</v>
+        <v>513</v>
       </c>
       <c r="C3" t="n">
-        <v>20.72999954223633</v>
+        <v>38.97063446044922</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01213827297773567</v>
+        <v>0.006667329411857124</v>
       </c>
       <c r="E3" t="n">
-        <v>20.98162593550833</v>
+        <v>39.2304645177861</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1030</v>
+        <v>143</v>
       </c>
       <c r="C4" t="n">
-        <v>20.5671272277832</v>
+        <v>139.5185546875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01238139170953263</v>
+        <v>0.001894972887308798</v>
       </c>
       <c r="E4" t="n">
-        <v>20.82177688633018</v>
+        <v>139.7829385659093</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>245</v>
+        <v>972</v>
       </c>
       <c r="C5" t="n">
-        <v>86.27027893066406</v>
+        <v>20.5671272277832</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003007303057106458</v>
+        <v>0.01238139170953263</v>
       </c>
       <c r="E5" t="n">
-        <v>86.52971980422969</v>
+        <v>20.82177688633018</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
         <v>87.23879241943359</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002959748167945932</v>
+        <v>0.002959748107245108</v>
       </c>
       <c r="E6" t="n">
-        <v>87.49699727547083</v>
+        <v>87.49699727017537</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.639231437359495</v>
+        <v>1.211892856712343</v>
       </c>
       <c r="C7" t="n">
         <v>140.5070037841797</v>
